--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19820" windowHeight="7860"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19815" windowHeight="7860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -147,11 +147,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,22 +458,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="31.36328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="69.6328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="3"/>
+    <col min="1" max="1" width="31.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="69.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="4"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -487,7 +487,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -498,7 +498,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProFailureInfo001.xlsx
@@ -60,9 +60,22 @@
       </rPr>
       <t>*</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>报告发布日期</t>
+    <r>
+      <t>报告发布日期（YYYY/MM/DD)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -144,14 +157,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,25 +475,25 @@
   <cols>
     <col min="1" max="1" width="31.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="69.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="4"/>
+    <col min="3" max="3" width="24.375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
